--- a/bulk_upload_module/templates/sample_user_access.xlsx
+++ b/bulk_upload_module/templates/sample_user_access.xlsx
@@ -582,6 +582,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Role" error="Please select a valid user role." type="list">
+      <formula1>"Student,Mentor,Coordinator,Department,Recruiter"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>